--- a/Central_NJ_Apartment_Comparison_WITH_TOUR_CLUSTERS_FINAL.xlsx
+++ b/Central_NJ_Apartment_Comparison_WITH_TOUR_CLUSTERS_FINAL.xlsx
@@ -545,8 +545,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:S55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -659,6 +659,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Validation Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -743,6 +748,11 @@
         </is>
       </c>
       <c r="R2" s="4" t="str"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -831,6 +841,11 @@
           <t>https://www.apartments.com/fairway-28-bridgewater-nj/3m3bv0f/</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -919,6 +934,11 @@
           <t>https://www.apartments.com/station-house-somerville-nj/0bzvy20/</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1007,6 +1027,11 @@
           <t>https://www.queensgateapts.com/floorplans</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1095,6 +1120,11 @@
           <t>https://www.redfin.com/zipcode/08854/2-bedroom-houses-for-rent</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1183,6 +1213,11 @@
           <t>https://www.premierdevelopment.com/central-nj/luxury-apartments/stone-bridge/</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1271,6 +1306,11 @@
           <t>https://www.premierdevelopment.com/central-nj/luxury-apartments/brookhaven-lofts/</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1363,6 +1403,11 @@
           <t>https://bestrentnj.com/Communities/Rivendell-at-Edison/</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1451,6 +1496,11 @@
           <t>https://www.zillow.com/apartments/watchung-nj/crystal-ridge-at-watchung/5Xj7JZ/</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1539,6 +1589,11 @@
           <t>https://www.liveatthelena.com/floorplans</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1627,6 +1682,11 @@
           <t>https://www.avaloncommunities.com/new-jersey/piscataway-apartments/avalon-piscataway/</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1715,6 +1775,11 @@
           <t>https://www.apartments.com/citizen-bound-brook-bound-brook-nj/39et2kd/</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1803,6 +1868,11 @@
           <t>https://www.theloftsmiddlesex.com/floorplans</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1891,6 +1961,11 @@
           <t>https://www.larkenassociates.com/residential-rentals/hillsborough-village-center</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1979,6 +2054,11 @@
           <t>https://www.premierdevelopment.com/central-nj/luxury-apartments/cedar-manor/</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2067,6 +2147,11 @@
           <t>https://www.apartments.com/sunnymeade-run-hillsborough-nj/2befhwb/</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2155,6 +2240,11 @@
           <t>https://bestrentnj.com/Communities/Pike-Run-Meadows/</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2243,6 +2333,11 @@
           <t>https://bestrentnj.com/Communities/Pike-Run-Village/</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2335,6 +2430,11 @@
           <t>https://bestrentnj.com/Communities/Rivendell-Heights/</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2423,6 +2523,11 @@
           <t>https://bestrentnj.com/Communities/Rivendell-Village/</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2511,6 +2616,11 @@
           <t>https://bestrentnj.com/Communities/Edison-Woods/</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2599,6 +2709,11 @@
           <t>https://bestrentnj.com/Communities/Mae-Brook-at-Renaissance/</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2687,6 +2802,11 @@
           <t>https://bestrentnj.com/Communities/Renaissance-Manor/</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2779,6 +2899,11 @@
           <t>https://bestrentnj.com/Communities/Blueberry-Village/</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2867,6 +2992,11 @@
           <t>https://www.apartments.com/raritan-riverside-raritan-nj/s1kqpf7/</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2955,6 +3085,11 @@
           <t>https://bestrentnj.com/Communities/Amwell-Terrace/</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3043,6 +3178,11 @@
           <t>https://mi-placehillsborough.com/floor-plans/</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3131,6 +3271,11 @@
           <t>https://www.bluehillnj.com/</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3215,6 +3360,11 @@
         </is>
       </c>
       <c r="R30" s="4" t="str"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3299,6 +3449,11 @@
         </is>
       </c>
       <c r="R31" s="4" t="str"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3387,6 +3542,11 @@
         </is>
       </c>
       <c r="R32" s="4" t="str"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3471,6 +3631,11 @@
         </is>
       </c>
       <c r="R33" s="4" t="str"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3555,6 +3720,11 @@
         </is>
       </c>
       <c r="R34" s="4" t="str"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3639,6 +3809,11 @@
         </is>
       </c>
       <c r="R35" s="4" t="str"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3723,6 +3898,11 @@
         </is>
       </c>
       <c r="R36" s="4" t="str"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3807,6 +3987,11 @@
         </is>
       </c>
       <c r="R37" s="4" t="str"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3891,6 +4076,11 @@
         </is>
       </c>
       <c r="R38" s="4" t="str"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3975,6 +4165,11 @@
         </is>
       </c>
       <c r="R39" s="4" t="str"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4059,6 +4254,11 @@
         </is>
       </c>
       <c r="R40" s="4" t="str"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4143,6 +4343,11 @@
         </is>
       </c>
       <c r="R41" s="4" t="str"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4227,6 +4432,11 @@
         </is>
       </c>
       <c r="R42" s="4" t="str"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -4311,6 +4521,11 @@
         </is>
       </c>
       <c r="R43" s="4" t="str"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4395,6 +4610,11 @@
         </is>
       </c>
       <c r="R44" s="4" t="str"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4479,6 +4699,11 @@
         </is>
       </c>
       <c r="R45" s="4" t="str"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4563,6 +4788,11 @@
         </is>
       </c>
       <c r="R46" s="4" t="str"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -4651,6 +4881,11 @@
           <t>https://therockwellgreenbrook.com/</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4739,6 +4974,11 @@
           <t>https://www.thekingsleynj.com/</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4831,6 +5071,11 @@
           <t>https://bestrentnj.com/Communities/Edison-Lights/</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4919,6 +5164,11 @@
           <t>https://bestrentnj.com/Communities/Woodbridge-Center-Plaza/</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5007,6 +5257,11 @@
           <t>https://bestrentnj.com/Communities/Woodbridge-Village/</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -5095,6 +5350,11 @@
           <t>https://bestrentnj.com/Communities/Beekman-Gardens/</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -5183,6 +5443,11 @@
           <t>https://bestrentnj.com/Communities/The-Glades-at-Beekman/</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -5271,6 +5536,11 @@
           <t>https://bestrentnj.com/Communities/Boulders-at-Beekman/</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -5357,6 +5627,11 @@
       <c r="R55" s="4" t="inlineStr">
         <is>
           <t>https://bestrentnj.com/Communities/North-Brunswick-Manor/</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Needs review</t>
         </is>
       </c>
     </row>
@@ -5400,8 +5675,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -5514,6 +5789,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Validation Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -5602,6 +5882,11 @@
           <t>https://www.apartments.com/fairway-28-bridgewater-nj/3m3bv0f/</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5690,6 +5975,11 @@
           <t>https://www.apartments.com/station-house-somerville-nj/0bzvy20/</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -5778,6 +6068,11 @@
           <t>https://www.premierdevelopment.com/central-nj/luxury-apartments/stone-bridge/</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5866,6 +6161,11 @@
           <t>https://www.apartments.com/raritan-riverside-raritan-nj/s1kqpf7/</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -5954,6 +6254,11 @@
           <t>https://www.liveatthelena.com/floorplans</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6042,6 +6347,11 @@
           <t>https://www.premierdevelopment.com/central-nj/luxury-apartments/brookhaven-lofts/</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -6130,6 +6440,11 @@
           <t>https://mi-placehillsborough.com/floor-plans/</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6218,6 +6533,11 @@
           <t>https://bestrentnj.com/Communities/Amwell-Terrace/</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -6306,6 +6626,11 @@
           <t>https://bestrentnj.com/Communities/Pike-Run-Meadows/</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6394,6 +6719,11 @@
           <t>https://bestrentnj.com/Communities/Pike-Run-Village/</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6482,6 +6812,11 @@
           <t>https://www.larkenassociates.com/residential-rentals/hillsborough-village-center</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -6570,6 +6905,11 @@
           <t>https://www.apartments.com/sunnymeade-run-hillsborough-nj/2befhwb/</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -6658,6 +6998,11 @@
           <t>https://www.redfin.com/zipcode/08854/2-bedroom-houses-for-rent</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -6746,6 +7091,11 @@
           <t>https://bestrentnj.com/Communities/Edison-Woods/</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -6838,6 +7188,11 @@
           <t>https://bestrentnj.com/Communities/Rivendell-Heights/</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6926,6 +7281,11 @@
           <t>https://bestrentnj.com/Communities/Rivendell-Village/</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7014,6 +7374,11 @@
           <t>https://www.avaloncommunities.com/new-jersey/piscataway-apartments/avalon-piscataway/</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7106,6 +7471,11 @@
           <t>https://bestrentnj.com/Communities/Rivendell-at-Edison/</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7194,6 +7564,11 @@
           <t>https://www.theloftsmiddlesex.com/floorplans</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -7282,6 +7657,11 @@
           <t>https://www.queensgateapts.com/floorplans</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7370,6 +7750,11 @@
           <t>https://www.bluehillnj.com/</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7458,6 +7843,11 @@
           <t>https://www.apartments.com/citizen-bound-brook-bound-brook-nj/39et2kd/</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7546,6 +7936,11 @@
           <t>https://www.zillow.com/apartments/watchung-nj/crystal-ridge-at-watchung/5Xj7JZ/</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -7634,6 +8029,11 @@
           <t>https://www.premierdevelopment.com/central-nj/luxury-apartments/cedar-manor/</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -7722,6 +8122,11 @@
           <t>https://bestrentnj.com/Communities/Mae-Brook-at-Renaissance/</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -7808,6 +8213,11 @@
       <c r="R27" s="4" t="inlineStr">
         <is>
           <t>https://bestrentnj.com/Communities/Renaissance-Manor/</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Needs review</t>
         </is>
       </c>
     </row>
@@ -7834,8 +8244,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
@@ -7855,6 +8265,11 @@
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Validation Status</t>
+        </is>
+      </c>
     </row>
     <row r="2"/>
     <row r="3">
@@ -7898,6 +8313,11 @@
           <t>Suggested combined tour</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7940,6 +8360,11 @@
           <t>Bridgewater + Raritan + Somerville</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7982,6 +8407,11 @@
           <t>Hillsborough + Belle Mead</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8024,6 +8454,11 @@
           <t>Edison + Piscataway + Middlesex/Dunellen + South Plainfield</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8066,6 +8501,11 @@
           <t>Bound Brook + South Bound Brook + Watchung + Green Brook</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8108,6 +8548,11 @@
           <t>Somerset + Franklin Park</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -8145,6 +8590,11 @@
           <t>New/North Brunswick + South Brunswick/Monmouth Junction</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -8182,6 +8632,11 @@
           <t>Woodbridge + Avenel</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="45" t="inlineStr">
@@ -8224,6 +8679,11 @@
           <t>Count</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8266,6 +8726,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8308,6 +8773,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8350,6 +8820,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8392,6 +8867,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8434,6 +8914,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8474,6 +8959,11 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>27</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Needs review</t>
         </is>
       </c>
     </row>
@@ -8492,6 +8982,11 @@
       <c r="F20" s="1" t="n"/>
       <c r="G20" s="1" t="n"/>
       <c r="H20" s="1" t="n"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Central_NJ_Apartment_Comparison_WITH_TOUR_CLUSTERS_FINAL.xlsx
+++ b/Central_NJ_Apartment_Comparison_WITH_TOUR_CLUSTERS_FINAL.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,21 @@
           <t>Validation Status</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Validation Notes</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Verified Source</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Last Checked</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -846,6 +861,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -939,6 +969,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1032,6 +1077,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1125,6 +1185,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1218,6 +1293,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1311,6 +1401,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1408,6 +1513,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1501,6 +1621,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1594,6 +1729,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1687,6 +1837,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1780,6 +1945,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1873,6 +2053,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1966,6 +2161,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2059,6 +2269,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2152,6 +2377,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2245,6 +2485,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2338,6 +2593,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2435,6 +2705,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2528,6 +2813,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2621,6 +2921,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2714,6 +3029,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2807,6 +3137,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2904,6 +3249,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2997,6 +3357,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3090,6 +3465,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3183,6 +3573,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3276,6 +3681,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3365,6 +3785,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3454,6 +3889,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3547,6 +3997,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3636,6 +4101,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3725,6 +4205,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3814,6 +4309,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3903,6 +4413,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3992,6 +4517,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4081,6 +4621,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4170,6 +4725,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4259,6 +4829,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4348,6 +4933,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4437,6 +5037,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -4526,6 +5141,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4615,6 +5245,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4704,6 +5349,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4793,6 +5453,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -4886,6 +5561,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4979,6 +5669,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5076,6 +5781,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5169,6 +5889,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5262,6 +5997,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -5355,6 +6105,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -5448,6 +6213,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -5541,6 +6321,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -5632,6 +6427,21 @@
       <c r="S55" t="inlineStr">
         <is>
           <t>Needs review</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
         </is>
       </c>
     </row>
@@ -5675,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5794,6 +6604,21 @@
           <t>Validation Status</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Validation Notes</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Verified Source</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Last Checked</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -5887,6 +6712,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5980,6 +6820,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6073,6 +6928,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6166,6 +7036,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -6259,6 +7144,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6352,6 +7252,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -6445,6 +7360,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6538,6 +7468,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -6631,6 +7576,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6724,6 +7684,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6817,6 +7792,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -6910,6 +7900,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -7003,6 +8008,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -7096,6 +8116,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7193,6 +8228,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -7286,6 +8336,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7379,6 +8444,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7476,6 +8556,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7569,6 +8664,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -7662,6 +8772,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7755,6 +8880,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7848,6 +8988,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7941,6 +9096,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -8034,6 +9204,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -8127,6 +9312,21 @@
           <t>Needs review</t>
         </is>
       </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -8218,6 +9418,21 @@
       <c r="S27" t="inlineStr">
         <is>
           <t>Needs review</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Insufficient live evidence</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Needs manual review</t>
         </is>
       </c>
     </row>
@@ -8244,7 +9459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -8270,6 +9485,21 @@
           <t>Validation Status</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Validation Notes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Verified Source</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Last Checked</t>
+        </is>
+      </c>
     </row>
     <row r="2"/>
     <row r="3">

--- a/Central_NJ_Apartment_Comparison_WITH_TOUR_CLUSTERS_FINAL.xlsx
+++ b/Central_NJ_Apartment_Comparison_WITH_TOUR_CLUSTERS_FINAL.xlsx
@@ -51,7 +51,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +93,11 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border/>
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,6 +225,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -785,7 +793,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>580 NJ-28, Bridgewater, NJ 08807</t>
         </is>
@@ -846,9 +854,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=580%20NJ-28%2C%20Bridgewater%2C%20NJ%2008807&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Target larger 2BR around 1,500 sqft; garage option. Strong fit if fixed total stays &lt;= $3,200.</t>
+      <c r="Q3" s="53" t="inlineStr">
+        <is>
+          <t>Pet-friendly community with luxury features and scenic views.</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr">
@@ -858,22 +866,22 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Fairway 28 | Address: 580 NJ-28, Bridgewater, NJ 08807 | Property Type: Apartment | Price: 2700 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'stainless steel appliances', 'Silestone countertops'] | Commute: 30 min or less | Leasing Office Phone: 908-541-0800 | Official Website: https://www.country-classics.com/fairway-28 | Notes: Pet-friendly community with luxury features and scenic views.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -893,7 +901,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>44 Veterans Memorial Dr E, Somerville, NJ 08876</t>
         </is>
@@ -954,9 +962,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=44%20Veterans%20Memorial%20Dr%20E%2C%20Somerville%2C%20NJ%2008876&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>Up to ~1,480 sqft; climate-controlled garage; excellent train/Main St access. Need exact unit total &lt;= $3,200.</t>
+      <c r="Q4" s="53" t="inlineStr">
+        <is>
+          <t>Pre-leasing available, located near NJ Transit train station.</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
@@ -966,22 +974,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Station House Somerville | Address: 44 Veterans Memorial Dr E, Somerville, NJ 08876 | Property Type: Apartment | Price: Not specified | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'private balconies'] | Commute: &lt;= 30 min | Leasing Office Phone: (908) 685-2100 | Official Website: https://stationhousesomerville.com | Notes: Pre-leasing available, located near NJ Transit train station.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1009,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>675 Tea St, Bound Brook, NJ 08805</t>
         </is>
@@ -1062,9 +1070,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=675%20Tea%20St%2C%20Bound%20Brook%2C%20NJ%2008805&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Focus on Carlton/Cadbury at the right price; garage available. Larger Durham likely over budget.</t>
+      <c r="Q5" s="53" t="inlineStr">
+        <is>
+          <t>Located near major highways and Bridgewater Commons Mall.</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -1074,22 +1082,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Queens Gate Apartments | Address: 675 Tea St, Bound Brook, NJ 08805 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'resident clubhouse', 'gated dog park', 'pet spa', 'outdoor grilling stations', 'fire pits'] | Commute: 30 min | Official Website: https://www.trulia.com/building/queens-gate-675-tea-st-bound-brook-nj-08805-1136269302 | Notes: Located near major highways and Bridgewater Commons Mall.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1117,7 @@
           <t>Priority / private</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>1 Possumtown Rd, Piscataway, NJ 08854</t>
         </is>
@@ -1170,9 +1178,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Possumtown%20Rd%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>Private condo; target 1,500+ sqft 2BR+den with garage. Check broker fee and renewal terms.</t>
+      <c r="Q6" s="53" t="inlineStr">
+        <is>
+          <t>Currently, there are 0 units available for rent.</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -1182,22 +1190,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Cedar Woods Condominium | Address: 1 Possumtown Rd, Piscataway, NJ 08854 | Property Type: Condominium | Price: N/A | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: N/A | Leasing Office Phone: 732-667-5046 | Official Website: https://www.apartments.com/building/cedar-woods-condominium-piscataway-nj/vpr8btf | Notes: Currently, there are 0 units available for rent.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1225,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>925 US-202, Raritan, NJ 08869</t>
         </is>
@@ -1278,9 +1286,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=925%20US-202%2C%20Raritan%2C%20NJ%2008869&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>Focus on 2BR+den/loft configurations that remain &lt;= $3,200 fixed.</t>
+      <c r="Q7" s="53" t="inlineStr">
+        <is>
+          <t>One month free on a new 13-month lease. All offers are for a limited time on select apartments.</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -1290,22 +1298,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Stone Bridge at Raritan | Address: 925 US-202, Raritan, NJ 08869 | Property Type: Apartment | Price: 2695 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'clubhouse', 'fitness center', 'business center', 'swimming pool'] | Commute: &lt;= 30 min | Leasing Office Phone: (732) 595-1313 | Official Website: https://www.gardencommunities.com/Properties/NJ/Somerset/Stone-Bridge-at-Raritan.aspx | Notes: One month free on a new 13-month lease. All offers are for a limited time on select apartments.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1333,7 @@
           <t>Visited / keep</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>233 US-206 N, Hillsborough Township, NJ 08844</t>
         </is>
@@ -1386,9 +1394,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=233%20US-206%20N%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>No elevator: only 1st floor. Best value seen: 1F 2BR+Study Corner ~1,440 sqft at $2,645. Outdoor trash; hallway odor noted.</t>
+      <c r="Q8" s="53" t="inlineStr">
+        <is>
+          <t>Property is off market and not currently listed for rent.</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
@@ -1398,22 +1406,22 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Brookhaven Lofts | Address: 233 US-206 N, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2045 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'swimming pool', 'clubhouse'] | Commute: unknown | Leasing Office Phone: 908-388-9107 | Official Website: https://www.premierdevelopment.com/central-nj/luxury-apartments/brookhaven-lofts | Notes: Property is off market and not currently listed for rent.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1441,7 @@
           <t>Visited / 1F or townhome only</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>10 Rivendell Way, Edison, NJ 08854</t>
         </is>
@@ -1498,9 +1506,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=10%20Rivendell%20Way%2C%20Edison%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>Millstone 2BR/2.5BA ~1,920 sqft around $2,850 is compelling; in-unit W/D and private parking; reviews/maintenance vary.</t>
+      <c r="Q9" s="53" t="inlineStr">
+        <is>
+          <t>Located in Edison, NJ, close to major routes and shopping.</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
@@ -1510,22 +1518,22 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell at Edison | Address: 10 Rivendell Way, Edison, NJ 08854 | Property Type: Apartment | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'central air conditioning', 'clubhouse membership', 'private patio/balcony', 'huge closets'] | Commute: 10 minutes walk to Edison Train Station | Official Website: https://bestrentnj.com/Communities/rivendell-at-edison | Notes: Located in Edison, NJ, close to major routes and shopping.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1553,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>1 Crystal Ridge Dr, Watchung, NJ 07069</t>
         </is>
@@ -1606,9 +1614,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Crystal%20Ridge%20Dr%2C%20Watchung%2C%20NJ%2007069&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>Only worth pursuing if a larger 2BR + garage/covered parking fits the fixed-cost cap.</t>
+      <c r="Q10" s="53" t="inlineStr">
+        <is>
+          <t>One Month Rent Free! - Move in by September 30 and receive one month rent free.</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -1618,22 +1626,22 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Crystal Ridge at Watchung | Address: 1 Crystal Ridge Dr, Watchung, NJ 07069 | Property Type: Apartment | Price: 3176 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Patio / balcony', 'Granite counters', 'Hardwood floors', 'Dishwasher', 'Pet friendly'] | Commute: Calculate commute | Leasing Office Phone: 866-782-1743 | Official Website: https://www.crystalridgeapartments.com | Notes: One Month Rent Free! - Move in by September 30 and receive one month rent free.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1661,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>100 River Park Dr, Raritan, NJ 08869</t>
         </is>
@@ -1714,9 +1722,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=100%20River%20Park%20Dr%2C%20Raritan%2C%20NJ%2008869&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>Only larger ~1,500 sqft 2BR plans; smaller units are not attractive enough.</t>
+      <c r="Q11" s="53" t="inlineStr">
+        <is>
+          <t>The Lena has rental units starting at $2451, which is within the budget. It offers 2-bedroom units and has in-unit laundry.</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -1726,22 +1734,22 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Lena | Address: 100 River Park Dr, Raritan, NJ 08869 | Property Type: Apartment | Price: 2451 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: (866) 981-8018 | Official Website: https://www.liveatthelena.com | Notes: The Lena has rental units starting at $2451, which is within the budget. It offers 2-bedroom units and has in-unit laundry.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1769,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>7000 Avalon Way, Piscataway, NJ 08854</t>
         </is>
@@ -1822,9 +1830,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=7000%20Avalon%20Way%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>Only larger ~1,600+ sqft layouts if total fixed cost remains reasonable.</t>
+      <c r="Q12" s="53" t="inlineStr">
+        <is>
+          <t>Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -1834,22 +1842,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Avalon Piscataway | Address: 7000 Avalon Way, Piscataway, NJ 08854 | Property Type: Apartment | Price: 3615 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'outdoor pool', 'landscaped courtyards', 'gas grills', 'WAG Pet Park', 'outdoor play area'] | Commute: 30 min | Official Website: https://www.trulia.com/building/avalon-piscataway-7000-avalon-way-piscataway-nj-08854-2748184769 | Notes: Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1877,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>507 E Main St, Bound Brook, NJ 08805</t>
         </is>
@@ -1930,9 +1938,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=507%20E%20Main%20St%2C%20Bound%20Brook%2C%20NJ%2008805&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>Covered parking/elevator/train access; space is smaller (~1,300s sqft). Historical water incident noted.</t>
+      <c r="Q13" s="53" t="inlineStr">
+        <is>
+          <t>Rented units available in the price range of $2,300 to $2,900.</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -1942,22 +1950,22 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Citizen Bound Brook | Address: 507 E Main St, Bound Brook, NJ 08805 | Property Type: Apartment | Price: 2386 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'business center', 'clubhouse'] | Commute: 30 min or less | Leasing Office Phone: (609) 526-3188 | Official Website: https://citizenboundbrook.com | Notes: Rented units available in the price range of $2,300 to $2,900.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1985,7 @@
           <t>Downsize option</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>150 Lincoln Blvd, Middlesex, NJ 08846</t>
         </is>
@@ -2038,9 +2046,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=150%20Lincoln%20Blvd%2C%20Middlesex%2C%20NJ%2008846&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>Garage + elevator + lower cost, but ~1,246 sqft is a major downsize.</t>
+      <c r="Q14" s="53" t="inlineStr">
+        <is>
+          <t>Property features 2 BR rental units available starting at $2150.</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
@@ -2050,22 +2058,22 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Lofts at Middlesex | Address: 150 Lincoln Blvd, Middlesex, NJ 08846 | Property Type: Apartment | Price: 2150 | Beds: 2 | Baths: 2 | Amenities: ['In-unit laundry', 'Garbage disposal', 'Managed community', 'Fitness center', 'Yoga studio', 'Cinema room', 'Billiards lounge', 'Private garages', 'Electric car chargers', 'Pet friendly'] | Commute: 30 min or less | Leasing Office Phone: (848) 289-1151 | Official Website: https://www.trulia.com/building/the-lofts-at-middlesex-150-lincoln-blvd-middlesex-nj-08846-2757889978 | Notes: Property features 2 BR rental units available starting at $2150.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2093,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>1 Housel Cir, Hillsborough Township, NJ 08844</t>
         </is>
@@ -2146,9 +2154,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Housel%20Cir%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>Elmore ~1,422 sqft + private garage; size is borderline but parking is strong.</t>
+      <c r="Q15" s="53" t="inlineStr">
+        <is>
+          <t>Located in the heart of Somerset County, this community features 1- and 2-bedroom apartments.</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr">
@@ -2158,22 +2166,22 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Hillsborough Village Center | Address: 1 Housel Cir, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2300 | Beds: 2 | Baths: 2.5 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'elevator', 'luxury LVT plank flooring', 'kitchens with island', 'quartz countertops', 'stainless steel appliances', 'patio/balcony'] | Commute: 30 min or less | Leasing Office Phone: (848) 315-2044 | Official Website: https://www.rentcafe.com/apartments/nj/hillsborough/hillsborough-village-center-llc/default.aspx | Notes: Located in the heart of Somerset County, this community features 1- and 2-bedroom apartments.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2201,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t>1800 Fir Ct, Somerset, NJ 08873</t>
         </is>
@@ -2254,9 +2262,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1800%20Fir%20Ct%2C%20Somerset%2C%20NJ%2008873&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>Upper + Loft ~1,650 sqft around $3,195 base; likely too close to cap after fixed fees; no strong covered-parking advantage.</t>
+      <c r="Q16" s="53" t="inlineStr">
+        <is>
+          <t>Cedar Manor offers 2 bedroom rentals starting at $3195/month.</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
@@ -2266,22 +2274,22 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Cedar Manor | Address: 1800 Fir Ct, Somerset, NJ 08873 | Property Type: Apartment | Price: 3195 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Leasing Office Phone: (732) 838-5617 | Official Website: http://www.gardencommunities.com/Properties/NJ/Somerset/Cedar-Manor.aspx | Notes: Cedar Manor offers 2 bedroom rentals starting at $3195/month.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2309,7 @@
           <t>Visited / downgraded</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>65 Gateway Blvd, Hillsborough Township, NJ 08844</t>
         </is>
@@ -2362,9 +2370,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=65%20Gateway%20Blvd%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>End Townhome ~1,975 sqft at $3,475. No amenity/parking fee; attached garage. Trash 2x/week, recycling every other week. Nice but not cheap enough.</t>
+      <c r="Q17" s="53" t="inlineStr">
+        <is>
+          <t>Property is within budget and has in-unit laundry and garbage disposal. Commute time is not specified.</t>
         </is>
       </c>
       <c r="R17" s="4" t="inlineStr">
@@ -2374,22 +2382,22 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Sunnymeade Run | Address: 65 Gateway Blvd, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2325 | Beds: 2 | Baths: 2.5 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: unknown | Leasing Office Phone: 908-739-6136 | Official Website: https://bestrentnj.com/Communities/sunnymeade-run | Notes: Property is within budget and has in-unit laundry and garbage disposal. Commute time is not specified.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2417,7 @@
           <t>Priority / tour</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>40 Pike Run Road, Belle Mead, NJ 08502</t>
         </is>
@@ -2470,9 +2478,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=40%20Pike%20Run%20Road%2C%20Belle%20Mead%2C%20NJ%2008502&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>Strong paper fit. Bellagio/Darsena 2BR ~1,920 sqft from ~$3,095; Como ~2,080 sqft from ~$3,195. In-unit W/D, private 1-car garage + driveway space. Townhouse-style internal stairs; no elevator. Trash included; verify dumpster location and Oct availability.</t>
+      <c r="Q18" s="53" t="inlineStr">
+        <is>
+          <t>1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
@@ -2482,22 +2490,22 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Pike Run Village | Address: 40 Pike Run Road, Belle Mead, NJ 08502 | Property Type: Apartment | Price: 3385 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Dishwasher', 'Garbage disposal', 'Patio / balcony', 'Pet friendly', 'Walk in closets', 'Gym'] | Commute: Calculate commute | Leasing Office Phone: 855-896-4784 | Official Website: https://www.apartmentlist.com/nj/belle-mead/pike-run-village--1 | Notes: 1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2525,7 @@
           <t>Second tier / tour with Meadows</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>40 Pike Run Road, Belle Mead, NJ 08502</t>
         </is>
@@ -2578,9 +2586,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=40%20Pike%20Run%20Road%2C%20Belle%20Mead%2C%20NJ%2008502&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>2BR options ~1,560–1,876 sqft; in-unit W/D. No elevator / walk-up; larger Cambridge layouts include finished basement. Surface parking; resident reviews more mixed than Meadows. Worth seeing while at same leasing office.</t>
+      <c r="Q19" s="53" t="inlineStr">
+        <is>
+          <t>1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="R19" s="4" t="inlineStr">
@@ -2590,22 +2598,22 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Pike Run Village | Address: 40 Pike Run Road, Belle Mead, NJ 08502 | Property Type: Apartment | Price: 3275 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Patio / balcony', 'Dishwasher', 'Pet friendly', 'Walk in closets', 'Gym'] | Commute: Calculate commute | Leasing Office Phone: 855-896-4784 | Official Website: https://www.apartmentlist.com/nj/belle-mead/pike-run-village--1 | Notes: 1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2633,7 @@
           <t>Visited / 1F or townhome only</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="53" t="inlineStr">
         <is>
           <t>10 Yosko Drive, Edison, NJ 08854</t>
         </is>
@@ -2690,9 +2698,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=10%20Yosko%20Drive%2C%20Edison%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>3BR Tappan II ~1,672 sqft from ~$3,095; in-unit W/D, private entrance/parking. Strong size-to-price candidate; verify exact Oct unit and all mandatory fees.</t>
+      <c r="Q20" s="53" t="inlineStr">
+        <is>
+          <t>Property meets user's rental profile.</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -2702,22 +2710,22 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell Heights | Address: 10 Yosko Drive, Edison, NJ 08854 | Property Type: Apartment | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Official Website: https://bestrentnj.com/Communities/rivendell-heights | Notes: Property meets user's rental profile.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2745,7 @@
           <t>Priority / tour</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>1100 Meadows Drive, Piscataway, NJ 08854</t>
         </is>
@@ -2798,9 +2806,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1100%20Meadows%20Drive%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>3BR Vale ~1,472 sqft from ~$2,995; Haven/Gates ~1,472–1,475 sqft around ~$3,085. In-unit W/D and private parking. Slightly under ideal 1,500 sqft but strong value.</t>
+      <c r="Q21" s="53" t="inlineStr">
+        <is>
+          <t>1 Month Free Rent</t>
         </is>
       </c>
       <c r="R21" s="4" t="inlineStr">
@@ -2810,22 +2818,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell Village | Address: 1100 Meadows Drive, Piscataway, NJ 08854 | Property Type: Apartment | Price: 3005 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'private parking', 'dishwasher'] | Commute: 30 min | Leasing Office Phone: 855-754-8642 | Official Website: https://readynjapartments.com/Rivendell-Village/The-Vale | Notes: 1 Month Free Rent</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2853,7 @@
           <t>Second tier</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>1000 US Highway 1, Edison, NJ 08817</t>
         </is>
@@ -2906,9 +2914,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1000%20US%20Highway%201%2C%20Edison%2C%20NJ%2008817&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>Special 2BR + Rec Room ~1,830 sqft from ~$2,800; in-unit W/D. Older community/product, but unusually strong space/price ratio. Verify exact unit condition and parking.</t>
+      <c r="Q22" s="53" t="inlineStr">
+        <is>
+          <t>Property meets all user requirements.</t>
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr">
@@ -2918,22 +2926,22 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Edison Woods | Address: 1000 US Highway 1, Edison, NJ 08817 | Property Type: Apartment | Price: 2564 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'on-site parking', 'balcony or patio', 'walk-in closets', 'central heating and air conditioning', 'pool', 'playground'] | Commute: &lt;= 30 min | Official Website: https://readynjapartments.com/Edison-Woods/2-Bedroom-with-Dining-Room | Notes: Property meets all user requirements.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2961,7 @@
           <t>Second tier</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>301 Renaissance Blvd East, North Brunswick, NJ 08902</t>
         </is>
@@ -3014,9 +3022,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=301%20Renaissance%20Blvd%20East%2C%20North%20Brunswick%2C%20NJ%2008902&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>York 3 2BR/2.5BA ~1,520 sqft; current pricing roughly upper-$2,700s/low-$2,800s depending listing; in-unit W/D. Good value but farther south. Same leasing center as Renaissance Manor.</t>
+      <c r="Q23" s="53" t="inlineStr">
+        <is>
+          <t>Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr">
@@ -3026,22 +3034,22 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Mae Brook at Renaissance | Address: 301 Renaissance Blvd East, North Brunswick, NJ 08902 | Property Type: Apartment | Price: 3510 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'swimming pool', 'playground'] | Commute: 30 min | Official Website: https://bestrentnj.com/Communities/mae-brook-at-renaissance | Notes: Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3069,7 @@
           <t>Second tier</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>301 Renaissance Blvd East, North Brunswick, NJ 08902</t>
         </is>
@@ -3122,9 +3130,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=301%20Renaissance%20Blvd%20East%2C%20North%20Brunswick%2C%20NJ%2008902&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>York 3 2BR/2.5BA ~1,520 sqft from about ~$2,760; in-unit W/D. Detached garages may be available for extra fee. Same leasing center as Mae Brook.</t>
+      <c r="Q24" s="53" t="inlineStr">
+        <is>
+          <t>1 Month Free Rent</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
@@ -3134,22 +3142,22 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Renaissance Manor | Address: 301 Renaissance Blvd East, North Brunswick, NJ 08902 | Property Type: Apartment | Price: 2365 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'on-site parking', 'private entrance', 'patio or balcony', 'central heating and air conditioning', 'walk-in closets', 'fully equipped eat-in kitchens', 'dishwasher', 'playground', 'swimming pools'] | Commute: 30 min or less | Leasing Office Phone: 844-877-5819 | Official Website: https://bestrentnj.com/Communities/renaissance-manor | Notes: 1 Month Free Rent</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3177,7 @@
           <t>Visited / exclude</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>11 Brunswick Ave, Edison, NJ 08817</t>
         </is>
@@ -3234,9 +3242,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=11%20Brunswick%20Ave%2C%20Edison%2C%20NJ%2008817&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>Hickory 2BR ~1,725 sqft from ~$3,010; Redwood 3BR ~1,715 sqft from ~$3,190. Strong size/price. Verify in-unit W/D and condition on the exact available unit. | Visited 2026-08-30: no in-unit washer/dryer; exclude.</t>
+      <c r="Q25" s="53" t="inlineStr">
+        <is>
+          <t>Property offers 2BR, 2BA options within the price range.</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr">
@@ -3246,22 +3254,22 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Blueberry Village | Address: 11 Brunswick Ave, Edison, NJ 08817 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'swimming pool'] | Commute: 30 min | Leasing Office Phone: 855-314-8540 | Official Website: https://www.bestrentnj.com/Communities/blueberry-village | Notes: Property offers 2BR, 2BA options within the price range.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3289,7 @@
           <t>Watch / smaller new build</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>21 Orlando Dr, Raritan, NJ 08869</t>
         </is>
@@ -3342,9 +3350,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=21%20Orlando%20Dr%2C%20Raritan%2C%20NJ%2008869&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>Brand-new 2026, available now. 2BR ~1,229–1,329 sqft; total monthly price around ~$3,050 before optional garage; garage ~$95–125. Good location/newness but much smaller than ideal.</t>
+      <c r="Q26" s="53" t="inlineStr">
+        <is>
+          <t>Total monthly price ranges from $3,050 to $3,375.</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
@@ -3354,22 +3362,22 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Raritan Riverside | Address: 21 Orlando Dr, Raritan, NJ 08869 | Property Type: Apartment | Price: 3050 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'on-site parking', 'pet friendly'] | Commute: 30 min or less | Leasing Office Phone: (609) 507-0928 | Official Website: https://raritanriverside.com | Notes: Total monthly price ranges from $3,050 to $3,375.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3397,7 @@
           <t>Conditional / special only</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>384 Amwell Road, Hillsborough, NJ 08844</t>
         </is>
@@ -3450,9 +3458,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=384%20Amwell%20Road%2C%20Hillsborough%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>Large layouts and full-size in-unit W/D; garages/driveways on select units. Current suitable large plans generally at or above the ~$3,200 cap. Call only if exact all-in cost or promotion makes sense.</t>
+      <c r="Q27" s="53" t="inlineStr">
+        <is>
+          <t>Property is within budget and meets bedroom and bathroom requirements.</t>
         </is>
       </c>
       <c r="R27" s="4" t="inlineStr">
@@ -3462,22 +3470,22 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Amwell Terrace | Address: 384 Amwell Road, Hillsborough, NJ 08844 | Property Type: Apartment | Price: 2395 | Beds: 2 | Baths: 2.5 | Amenities: ['In-unit laundry', 'Garbage disposal', 'Managed community'] | Commute: 30 min | Leasing Office Phone: 844-816-3530 | Official Website: https://www.apartments.com/amwell-terrace-hillsborough-nj/jz1pgp4 | Notes: Property is within budget and meets bedroom and bathroom requirements.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3505,7 @@
           <t>New development / watch</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="53" t="inlineStr">
         <is>
           <t>4 Campus Dr, Hillsborough, NJ 08844</t>
         </is>
@@ -3558,9 +3566,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=4%20Campus%20Dr%2C%20Hillsborough%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>96-unit new development with 1–3BR; pre-leasing expected in 2026 and first occupancy targeted for fall. Potentially attractive larger layouts; pricing, elevator, W/D and exact move-in inventory still need confirmation.</t>
+      <c r="Q28" s="53" t="inlineStr">
+        <is>
+          <t>Property matches user's rental profile.</t>
         </is>
       </c>
       <c r="R28" s="4" t="inlineStr">
@@ -3570,22 +3578,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Mi-Place at Hillsborough | Address: 4 Campus Dr, Hillsborough, NJ 08844 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Official Website: official website | Notes: Property matches user's rental profile.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3613,7 @@
           <t>Future only / too late for Oct</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="53" t="inlineStr">
         <is>
           <t>8000 Schindler Drive, Watchung, NJ 07069</t>
         </is>
@@ -3666,9 +3674,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=8000%20Schindler%20Drive%2C%20Watchung%2C%20NJ%2007069&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>New 1–2BR luxury development; official site says rentals arrive soon. Strong amenities/elevators/garages, but first units expected late 2026, so not dependable for an Oct move. Keep for future monitoring.</t>
+      <c r="Q29" s="53" t="inlineStr">
+        <is>
+          <t>Affordable housing lottery; preference for applicants who live and/or work in Housing Region 3.</t>
         </is>
       </c>
       <c r="R29" s="4" t="inlineStr">
@@ -3678,22 +3686,22 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Blue Hill | Address: 8000 Schindler Drive, Watchung, NJ 07069 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'outdoor pool', 'fitness center'] | Commute: &lt;= 30 min | Official Website: https://www.bluehillnj.com | Notes: Affordable housing lottery; preference for applicants who live and/or work in Housing Region 3.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3713,7 +3721,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="53" t="inlineStr">
         <is>
           <t>100 Bellis Ct, Bridgewater, NJ 08807</t>
         </is>
@@ -3774,30 +3782,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=100%20Bellis%20Ct%2C%20Bridgewater%2C%20NJ%2008807&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>Too small for the tradeoff; maintenance/management concerns.</t>
+      <c r="Q30" s="53" t="inlineStr">
+        <is>
+          <t>Two Weeks Free on a signed 13 month lease!</t>
         </is>
       </c>
       <c r="R30" s="4" t="str"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Bridgewater Square | Address: 100 Bellis Ct, Bridgewater, NJ 08807 | Property Type: Apartment | Price: 2479 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min or less | Leasing Office Phone: (908) 219-7301 | Official Website: https://www.apartments.com/bridgewater-square-two-weeks-free-bridgewater-nj/zk2g6dz | Notes: Two Weeks Free on a signed 13 month lease!</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3825,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="53" t="inlineStr">
         <is>
           <t>2800 New Brunswick Ave, Piscataway, NJ 08854</t>
         </is>
@@ -3878,30 +3886,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=2800%20New%20Brunswick%20Ave%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>Maintenance/AC review concerns; no compelling advantage.</t>
+      <c r="Q31" s="53" t="inlineStr">
+        <is>
+          <t>Units available within budget and meet all user preferences.</t>
         </is>
       </c>
       <c r="R31" s="4" t="str"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Aspen Court Apartment Homes | Address: 2800 New Brunswick Ave, Piscataway, NJ 08854 | Property Type: Apartments | Price: 2834 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: (848) 893-7112 | Official Website: https://www.apartments.com/aspen-court-apartments-piscataway-nj/j4zx6h5 | Notes: Units available within budget and meet all user preferences.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3929,7 @@
           <t>Visited / 1F or townhome only</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="53" t="inlineStr">
         <is>
           <t>116 Meadows Dr, Piscataway, NJ 08854</t>
         </is>
@@ -3986,30 +3994,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=116%20Meadows%20Dr%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>Even larger plans are too small for the price; maintenance concerns.</t>
+      <c r="Q32" s="53" t="inlineStr">
+        <is>
+          <t>Price range is $2,795 - $3,495, but falls within the user's budget.</t>
         </is>
       </c>
       <c r="R32" s="4" t="str"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell Meadows | Address: 116 Meadows Dr, Piscataway, NJ 08854 | Property Type: Apartment | Price: 2795 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Leasing Office Phone: (848) 359-5153 | Official Website: https://www.apartmenthomeliving.com/apartment-finder/Rivendell-Meadows-Piscataway-NJ-08854-27410139 | Notes: Price range is $2,795 - $3,495, but falls within the user's budget.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4037,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="53" t="inlineStr">
         <is>
           <t>100 S Washington Ave, Dunellen, NJ 08812</t>
         </is>
@@ -4090,30 +4098,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=100%20S%20Washington%20Ave%2C%20Dunellen%2C%20NJ%2008812&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>2BR floor plans too small for your needs.</t>
+      <c r="Q33" s="53" t="inlineStr">
+        <is>
+          <t>Verified listing, available September 10, 2026.</t>
         </is>
       </c>
       <c r="R33" s="4" t="str"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Nell at Dunellen Station | Address: 100 S Washington Ave, Dunellen, NJ 08812 | Property Type: Apartment | Price: 2891 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'pool'] | Commute: &lt;= 30 min | Leasing Office Phone: (908) 860-8380 | Official Website: https://www.livethenell.com | Notes: Verified listing, available September 10, 2026.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4141,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="53" t="inlineStr">
         <is>
           <t>100 Rutgers Blvd, Somerset, NJ 08873</t>
         </is>
@@ -4194,30 +4202,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=100%20Rutgers%20Blvd%2C%20Somerset%2C%20NJ%2008873&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>Large layouts exist, but management/move-out/parking concerns and no covered-parking advantage.</t>
+      <c r="Q34" s="53" t="inlineStr">
+        <is>
+          <t>One month free on a new 13-month lease. All offers are for a limited time on select apartments.</t>
         </is>
       </c>
       <c r="R34" s="4" t="str"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Summerfields Lofts | Address: 100 Rutgers Blvd, Somerset, NJ 08873 | Property Type: Apartment | Price: 3065 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'pet-friendly', 'gas heating', 'playground'] | Commute: 30 min | Leasing Office Phone: (732) 936-7383 | Official Website: https://www.gardencommunities.com/Properties/NJ/Somerset/Summerfields-Lofts.aspx | Notes: One month free on a new 13-month lease. All offers are for a limited time on select apartments.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4245,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="53" t="inlineStr">
         <is>
           <t>200 Green Hill Manor Dr, Franklin Park, NJ 08823</t>
         </is>
@@ -4298,30 +4306,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=200%20Green%20Hill%20Manor%20Dr%2C%20Franklin%20Park%2C%20NJ%2008823&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>Mixed/weak maintenance feedback and no strong parking advantage.</t>
+      <c r="Q35" s="53" t="inlineStr">
+        <is>
+          <t>One month free on a new 13-month lease. All offers are on select apartments for a limited time.</t>
         </is>
       </c>
       <c r="R35" s="4" t="str"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Green Hill Luxury Rentals | Address: 200 Green Hill Manor Dr, Franklin Park, NJ 08823 | Property Type: Apartment | Price: 2385 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: (732) 479-1997 | Official Website: https://www.gardencommunities.com/Properties/NJ/Somerset/Green-Hill-Luxury-Rentals.aspx | Notes: One month free on a new 13-month lease. All offers are on select apartments for a limited time.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4349,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="53" t="inlineStr">
         <is>
           <t>22 Robeson St, Somerville, NJ 08876</t>
         </is>
@@ -4402,30 +4410,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=22%20Robeson%20St%2C%20Somerville%2C%20NJ%2008876&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>Good location but not enough space/cost advantage after fees.</t>
+      <c r="Q36" s="53" t="inlineStr">
+        <is>
+          <t>Price range is $2,470 - $3,615 per month. Apply by 8/31 for 1 month off!</t>
         </is>
       </c>
       <c r="R36" s="4" t="str"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Avalon Somerville Station | Address: 22 Robeson St, Somerville, NJ 08876 | Property Type: Apartment | Price: 2470 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Garbage disposal', 'Dishwasher', 'Patio / balcony', 'Hardwood floors', 'Pet friendly', '24hr maintenance'] | Commute: Calculate commute | Leasing Office Phone: (640) 214-3934 | Official Website: https://www.apartmentlist.com/nj/somerville/avalon-somerville-station | Notes: Price range is $2,470 - $3,615 per month. Apply by 8/31 for 1 month off!</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4445,9 +4453,9 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>11 US-1, New Brunswick, NJ 08901</t>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>11 US Highway 1, New Brunswick, NJ 08901</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -4506,30 +4514,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=11%20US-1%2C%20New%20Brunswick%2C%20NJ%2008901&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>Around 1,300 sqft at a relatively high price; weak value for your needs.</t>
+      <c r="Q37" s="53" t="inlineStr">
+        <is>
+          <t>Units available starting at $2,598/month, with some units having in-unit laundry.</t>
         </is>
       </c>
       <c r="R37" s="4" t="str"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Edge at Raritan Heights | Address: 11 US Highway 1, New Brunswick, NJ 08901 | Property Type: Apartment | Price: 2598 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'game room'] | Commute: unknown | Leasing Office Phone: 848-283-5972 | Official Website: https://www.edgewoodproperties.com/properties/the-edge-at-raritan-heights | Notes: Units available starting at $2,598/month, with some units having in-unit laundry.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4557,7 @@
           <t>Exclude unless special</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="53" t="inlineStr">
         <is>
           <t>1 Schindler Ct, Hillsborough Township, NJ 08844</t>
         </is>
@@ -4610,30 +4618,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Schindler%20Ct%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>Larger garage units generally do not save enough vs current home. Reconsider only with a large discount.</t>
+      <c r="Q38" s="53" t="inlineStr">
+        <is>
+          <t>The Hillmont is located in Hillsborough, NJ, which is within commuting distance to Bridgewater/Somerset.</t>
         </is>
       </c>
       <c r="R38" s="4" t="str"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Hillmont | Address: 1 Schindler Ct, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2300 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: (201) 987-9148 | Official Website: https://www.zillow.com/apartments/hillsborough-nj/the-hillmont/CgJ9Xg | Notes: The Hillmont is located in Hillsborough, NJ, which is within commuting distance to Bridgewater/Somerset.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4661,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="53" t="inlineStr">
         <is>
           <t>220 Lincoln Blvd, Middlesex, NJ 08846</t>
         </is>
@@ -4714,30 +4722,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=220%20Lincoln%20Blvd%2C%20Middlesex%2C%20NJ%2008846&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>Covered parking/elevator are good, but max suitable 2BR size is around 1,200 sqft.</t>
+      <c r="Q39" s="53" t="inlineStr">
+        <is>
+          <t>The property meets the user's rental profile.</t>
         </is>
       </c>
       <c r="R39" s="4" t="str"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The View at Middlesex | Address: 220 Lincoln Blvd, Middlesex, NJ 08846 | Property Type: Apartment | Price: 2750 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: unknown | Leasing Office Phone: (908) 493-5542 | Official Website: https://www.middlesexview.com | Notes: The property meets the user's rental profile.</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4765,7 @@
           <t>Exclude unless special</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="53" t="inlineStr">
         <is>
           <t>175 W Main St, Somerville, NJ 08876</t>
         </is>
@@ -4818,30 +4826,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=175%20W%20Main%20St%2C%20Somerville%2C%20NJ%2008876&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>Good reputation/location, but larger 2BR pricing/size does not beat stronger options.</t>
+      <c r="Q40" s="53" t="inlineStr">
+        <is>
+          <t>Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="R40" s="4" t="str"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Edge at Main | Address: 175 W Main St, Somerville, NJ 08876 | Property Type: Apartment | Price: 4098 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: N/A | Leasing Office Phone: (201) 733-4234 | Official Website: https://www.theedgeatmain.com | Notes: Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4869,7 @@
           <t>55+ eligibility</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="53" t="inlineStr">
         <is>
           <t>112 Schoolhouse Rd, Somerset, NJ 08873</t>
         </is>
@@ -4922,30 +4930,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=112%20Schoolhouse%20Rd%2C%20Somerset%2C%20NJ%2008873&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>Active-adult 55+ community; exclude unless household meets eligibility.</t>
+      <c r="Q41" s="53" t="inlineStr">
+        <is>
+          <t>Price exceeds max budget; commute time not specified.</t>
         </is>
       </c>
       <c r="R41" s="4" t="str"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Enclave at Canal Walk | Address: 112 Schoolhouse Rd, Somerset, NJ 08873 | Property Type: conventional | Price: 3295 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'business center', 'state-of-the-art theater', 'pet friendly'] | Commute: unknown | Leasing Office Phone: 908.429.3000 | Official Website: https://www.premierdevelopment.com/central-nj/luxury-apartments/the-enclave | Notes: Price exceeds max budget; commute time not specified.</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4973,7 @@
           <t>Visited / exclude</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="53" t="inlineStr">
         <is>
           <t>13 Downbury Ct, Hillsborough Township, NJ 08844</t>
         </is>
@@ -5026,30 +5034,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=13%20Downbury%20Ct%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>Visited in person; overall environment was strongly disliked.</t>
+      <c r="Q42" s="53" t="inlineStr">
+        <is>
+          <t>Monthly rent is within budget.</t>
         </is>
       </c>
       <c r="R42" s="4" t="str"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: New Center Greens Garden Apartments | Address: 13 Downbury Ct, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2835 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Leasing Office Phone: (833) 985-3807 | Official Website: https://www.apartments.com/new-center-greens-garden-apartments-hillsborough-nj/y1rz2ev | Notes: Monthly rent is within budget.</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5077,7 @@
           <t>Watch only</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="53" t="inlineStr">
         <is>
           <t>193 Forest Dr, Piscataway, NJ 08854</t>
         </is>
@@ -5130,30 +5138,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=193%20Forest%20Dr%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>Private condo value can be good, but surface parking/access/AC transparency weaker than Cedar Woods.</t>
+      <c r="Q43" s="53" t="inlineStr">
+        <is>
+          <t>Property meets all user requirements.</t>
         </is>
       </c>
       <c r="R43" s="4" t="str"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Birch Glen Condominiums | Address: 193 Forest Dr, Piscataway, NJ 08854 | Property Type: Apartment | Price: 2750 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'playgrounds', 'tennis', 'pool', 'clubhouse'] | Commute: 30 min or less | Leasing Office Phone: (908) 895-6910 | Official Website: https://www.apartmenthomeliving.com/apartment-finder/BIRCH-GLEN-Piscataway-NJ-08854-24718328 | Notes: Property meets all user requirements.</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5181,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="53" t="inlineStr">
         <is>
           <t>153 Main St, South Bound Brook, NJ 08880</t>
         </is>
@@ -5234,30 +5242,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=153%20Main%20St%2C%20South%20Bound%20Brook%2C%20NJ%2008880&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>Large on paper with garage/storage included in listed sqft; management/move-out concerns.</t>
+      <c r="Q44" s="53" t="inlineStr">
+        <is>
+          <t>Price range is within budget, but baths exceed preference.</t>
         </is>
       </c>
       <c r="R44" s="4" t="str"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Gramercy Townhomes | Address: 153 Main St, South Bound Brook, NJ 08880 | Property Type: Apartment | Price: 3250 | Beds: 2 | Baths: 2.5 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', '2-car garage'] | Commute: 30 min | Leasing Office Phone: SKG MANAGEMENT | Official Website: https://www.landmarkcompanies.net/portfolio/gramercy-townhomes | Notes: Price range is within budget, but baths exceed preference.</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5285,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="53" t="inlineStr">
         <is>
           <t>100 Hamilton St, Bound Brook, NJ 08805</t>
         </is>
@@ -5338,30 +5346,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=100%20Hamilton%20St%2C%20Bound%20Brook%2C%20NJ%2008805&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>New, train-adjacent and garage available, but 2BR plans are only around ~1,022 sqft.</t>
+      <c r="Q45" s="53" t="inlineStr">
+        <is>
+          <t>The property is slightly above the maximum budget of $3200.</t>
         </is>
       </c>
       <c r="R45" s="4" t="str"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Rail at Bound Brook | Address: 100 Hamilton St, Bound Brook, NJ 08805 | Property Type: Apartment | Price: 3350 | Beds: 2 | Baths: 1 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: (848) 283-5656 | Official Website: https://www.apartments.com/the-rail-at-bound-brook-bound-brook-nj/6bxt4vv | Notes: The property is slightly above the maximum budget of $3200.</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5389,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="53" t="inlineStr">
         <is>
           <t>1636 Stelton Rd, Piscataway, NJ 08854</t>
         </is>
@@ -5442,30 +5450,30 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1636%20Stelton%20Rd%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>Larger units approach current rent while offering much less living space.</t>
+      <c r="Q46" s="53" t="inlineStr">
+        <is>
+          <t>Does not offer in-unit laundry.</t>
         </is>
       </c>
       <c r="R46" s="4" t="str"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Villas at Fairway | Address: 1636 Stelton Rd, Piscataway, NJ 08854 | Property Type: Apartment | Price: 3229 | Beds: 2 | Baths: 2 | Amenities: ['managed community', 'garbage disposal'] | Commute: 30+ min | Leasing Office Phone: 732-624-6296 | Official Website: https://www.apartments.com/the-villas-at-fairway-piscataway-nj/7v5y4jw | Notes: Does not offer in-unit laundry.</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5493,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="53" t="inlineStr">
         <is>
           <t>76 Greenbrook Rd, Green Brook Township, NJ 08812</t>
         </is>
@@ -5546,9 +5554,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=76%20Greenbrook%20Rd%2C%20Green%20Brook%20Township%2C%20NJ%2008812&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>Brand-new, pre-leasing for Fall 2026 with elevator and in-unit W/D, but largest 2BR found is only ~1,180 sqft. Too much of a size compromise.</t>
+      <c r="Q47" s="53" t="inlineStr">
+        <is>
+          <t>Property meets user's rental profile.</t>
         </is>
       </c>
       <c r="R47" s="4" t="inlineStr">
@@ -5558,22 +5566,22 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Rockwell | Address: 76 Greenbrook Rd, Green Brook Township, NJ 08812 | Property Type: Apartment | Price: 2715 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Leasing Office Phone: 908-293-7352 | Official Website: https://www.apartmenthomeliving.com/green-brook-nj/apartments-for-rent/2-bedroom | Notes: Property meets user's rental profile.</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5601,7 @@
           <t>Exclude unless major special</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="53" t="inlineStr">
         <is>
           <t>1111 Durham Ave, South Plainfield, NJ 07080</t>
         </is>
@@ -5654,9 +5662,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1111%20Durham%20Ave%2C%20South%20Plainfield%2C%20NJ%2007080&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>Large 2BR/duplex layouts exist, but suitable larger units price above the target; smaller 2BRs do not offer enough space. Keep excluded unless a major promotion changes the math.</t>
+      <c r="Q48" s="53" t="inlineStr">
+        <is>
+          <t>Price is within budget, has 2 bedrooms and 2 bathrooms, but does not offer in-unit laundry.</t>
         </is>
       </c>
       <c r="R48" s="4" t="inlineStr">
@@ -5666,22 +5674,22 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Kingsley | Address: 1111 Durham Ave, South Plainfield, NJ 07080 | Property Type: Apartment | Price: 3177 | Beds: 2 | Baths: 2 | Amenities: ['Patio / Balcony', 'Pet Friendly', 'Garage', 'Walk In Closets', 'Gym', 'Coffee Bar'] | Commute: Calculate commute | Leasing Office Phone: 732-820-5596 | Official Website: https://www.edgewoodproperties.com/properties/the-kingsley | Notes: Price is within budget, has 2 bedrooms and 2 bathrooms, but does not offer in-unit laundry.</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5709,7 @@
           <t>Visited / 1F or townhome only</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="53" t="inlineStr">
         <is>
           <t>3014 Yosko Drive, Edison, NJ 08817</t>
         </is>
@@ -5766,9 +5774,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=3014%20Yosko%20Drive%2C%20Edison%2C%20NJ%2008817&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>Suitable 2BR options are too small or too expensive relative to Rivendell/Edison Woods alternatives. No compelling value advantage.</t>
+      <c r="Q49" s="53" t="inlineStr">
+        <is>
+          <t>Edison Lights offers a variety of attractive layouts including 2 bedroom duplexes.</t>
         </is>
       </c>
       <c r="R49" s="4" t="inlineStr">
@@ -5778,22 +5786,22 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Edison Lights | Address: 3014 Yosko Drive, Edison, NJ 08817 | Property Type: conventional | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Official Website: https://bestrentnj.com/Communities/Edison-Lights | Notes: Edison Lights offers a variety of attractive layouts including 2 bedroom duplexes.</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5821,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="53" t="inlineStr">
         <is>
           <t>1605 Plaza Drive, Woodbridge, NJ 07095</t>
         </is>
@@ -5874,9 +5882,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1605%20Plaza%20Drive%2C%20Woodbridge%2C%20NJ%2007095&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>2BR plans mostly ~1,060–1,110 sqft; 3BR townhouse ~1,805 sqft is around ~$3,480. In-unit W/D is good, but size/price/location tradeoff is weak.</t>
+      <c r="Q50" s="53" t="inlineStr">
+        <is>
+          <t>Managed community by Middlesex Management, available now.</t>
         </is>
       </c>
       <c r="R50" s="4" t="inlineStr">
@@ -5886,22 +5894,22 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Woodbridge Center Plaza | Address: 1605 Plaza Drive, Woodbridge, NJ 07095 | Property Type: Apartment | Price: 2465 | Beds: 2 | Baths: 2 | Amenities: ['In-unit laundry', 'Garbage disposal', 'Air conditioning', 'Cable ready', 'Heating', 'Tub/Shower', 'Washer/Dryer', 'Dishwasher', 'Eat-in kitchen', 'Range', 'Carpet', 'Hardwood floors'] | Commute: &lt;= 30 min | Leasing Office Phone: (848) 283-6906 | Official Website: https://www.apartmenthomeliving.com/apartment-finder/Woodbridge-Center-Plaza-Woodbridge-NJ-07095-27378989 | Notes: Managed community by Middlesex Management, available now.</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5929,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="53" t="inlineStr">
         <is>
           <t>22 South Village Drive, Avenel, NJ 07001</t>
         </is>
@@ -5982,9 +5990,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=22%20South%20Village%20Drive%2C%20Avenel%2C%20NJ%2007001&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>2BR with rec room can reach ~1,465 sqft at a reasonable rent, but community advertises a laundry center rather than in-unit W/D. Fails the in-unit laundry requirement.</t>
+      <c r="Q51" s="53" t="inlineStr">
+        <is>
+          <t>Price is within budget and meets all user preferences.</t>
         </is>
       </c>
       <c r="R51" s="4" t="inlineStr">
@@ -5994,22 +6002,22 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Woodbridge Village | Address: 22 South Village Drive, Avenel, NJ 07001 | Property Type: Apartment | Price: 1680 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: 855-332-2166 | Official Website: https://bestrentnj.com/Communities/woodbridge-village | Notes: Price is within budget and meets all user preferences.</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6037,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="53" t="inlineStr">
         <is>
           <t>348 Gemini Drive, Hillsborough, NJ 08844</t>
         </is>
@@ -6090,9 +6098,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=348%20Gemini%20Drive%2C%20Hillsborough%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>Largest 2BR duplex ~1,280 sqft and laundry rooms are onsite rather than in-unit. Too small and misses the in-unit W/D requirement.</t>
+      <c r="Q52" s="53" t="inlineStr">
+        <is>
+          <t>Does not provide in-unit laundry; on-site laundry facilities available for shared resident use.</t>
         </is>
       </c>
       <c r="R52" s="4" t="inlineStr">
@@ -6102,22 +6110,22 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Beekman Gardens | Address: 348 Gemini Drive, Hillsborough, NJ 08844 | Property Type: Apartment | Beds: 2 | Baths: 1.5 | Amenities: ['heat included', 'hot water included', 'hardwood floors', 'balcony', 'kitchen with microwave oven', 'ample on-site parking', 'on-site tennis courts', 'on-site basketball courts', 'on-site handball courts', 'playgrounds', 'clean decorated laundry rooms', 'on-site maintenance team'] | Official Website: https://www.apartments.com/beekman-gardens-hillsborough-nj/n00p7dm | Notes: Does not provide in-unit laundry; on-site laundry facilities available for shared resident use.</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6145,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="53" t="inlineStr">
         <is>
           <t>307 Howell Court, Monmouth Junction, NJ 08852</t>
         </is>
@@ -6198,9 +6206,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=307%20Howell%20Court%2C%20Monmouth%20Junction%2C%20NJ%2008852&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>Brand-new. 2BR ~1,315 sqft from ~$3,145; 3BR ~1,560 sqft from ~$3,445. The layout that meets the size target is above budget; weaker value than Pike Run.</t>
+      <c r="Q53" s="53" t="inlineStr">
+        <is>
+          <t>Price is slightly above the maximum budget but includes in-unit laundry and is in a managed community.</t>
         </is>
       </c>
       <c r="R53" s="4" t="inlineStr">
@@ -6210,22 +6218,22 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Glades at Beekman | Address: 307 Howell Court, Monmouth Junction, NJ 08852 | Property Type: Apartment | Price: 3145 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min or less | Leasing Office Phone: 833-495-0752 | Official Website: https://www.apartments.com/the-glades-at-beekman-monmouth-junction-nj/m119f6j | Notes: Price is slightly above the maximum budget but includes in-unit laundry and is in a managed community.</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6253,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="53" t="inlineStr">
         <is>
           <t>112 Romeo Court, Monmouth Junction, NJ 08852</t>
         </is>
@@ -6306,9 +6314,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=112%20Romeo%20Court%2C%20Monmouth%20Junction%2C%20NJ%2008852&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>In-unit W/D is a plus, but suitable 2BR layouts top out around ~1,290 sqft. Not enough space for this move.</t>
+      <c r="Q54" s="53" t="inlineStr">
+        <is>
+          <t>Located in desirable South Brunswick, convenient to Route 1 shopping and dining.</t>
         </is>
       </c>
       <c r="R54" s="4" t="inlineStr">
@@ -6318,22 +6326,22 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Boulders at Beekman | Address: 112 Romeo Court, Monmouth Junction, NJ 08852 | Property Type: Apartment | Price: 3145 | Beds: 2 | Baths: 2.5 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'clubhouse'] | Commute: 30 min | Leasing Office Phone: (848) 279-1442 | Official Website: https://livebeekman.com | Notes: Located in desirable South Brunswick, convenient to Route 1 shopping and dining.</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6361,7 @@
           <t>Exclude</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="53" t="inlineStr">
         <is>
           <t>2880 Birchwood Court, North Brunswick, NJ 08902</t>
         </is>
@@ -6414,9 +6422,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=2880%20Birchwood%20Court%2C%20North%20Brunswick%2C%20NJ%2008902&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>2BR townhouse can reach ~1,500 sqft at a reasonable price, but property advertises shared laundry facilities and does not list in-unit W/D. Fails the laundry requirement.</t>
+      <c r="Q55" s="53" t="inlineStr">
+        <is>
+          <t>Located directly off Route 1, yet nestled in a quiet, park-like setting.</t>
         </is>
       </c>
       <c r="R55" s="4" t="inlineStr">
@@ -6426,22 +6434,22 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: North Brunswick Manor | Address: 2880 Birchwood Court, North Brunswick, NJ 08902 | Property Type: Apartment | Price: 1955 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'clubhouse', 'pool', 'tennis courts', 'beach volleyball courts'] | Commute: &lt;= 30 min | Leasing Office Phone: 866-756-4218 | Official Website: https://bestrentnj.com/Communities/north-brunswick-manor | Notes: Located directly off Route 1, yet nestled in a quiet, park-like setting.</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6644,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>580 NJ-28, Bridgewater, NJ 08807</t>
         </is>
@@ -6697,9 +6705,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=580%20NJ-28%2C%20Bridgewater%2C%20NJ%2008807&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>Target larger 2BR around 1,500 sqft; garage option. Strong fit if fixed total stays &lt;= $3,200.</t>
+      <c r="Q2" s="53" t="inlineStr">
+        <is>
+          <t>Award-winning, pet-friendly community with luxury features.</t>
         </is>
       </c>
       <c r="R2" s="4" t="inlineStr">
@@ -6709,22 +6717,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Fairway 28 | Address: 580 NJ-28, Bridgewater, NJ 08807 | Property Type: Apartment | Price: 2700 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'community room', 'stainless steel appliances', 'Silestone countertops'] | Commute: 30 min or less | Leasing Office Phone: 908-541-0800 | Official Website: https://www.country-classics.com/fairway-28 | Notes: Award-winning, pet-friendly community with luxury features.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6752,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>44 Veterans Memorial Dr E, Somerville, NJ 08876</t>
         </is>
@@ -6805,9 +6813,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=44%20Veterans%20Memorial%20Dr%20E%2C%20Somerville%2C%20NJ%2008876&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Up to ~1,480 sqft; climate-controlled garage; excellent train/Main St access. Need exact unit total &lt;= $3,200.</t>
+      <c r="Q3" s="53" t="inlineStr">
+        <is>
+          <t>Pre-leasing available, ultra-luxury apartments.</t>
         </is>
       </c>
       <c r="R3" s="4" t="inlineStr">
@@ -6817,22 +6825,22 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Station House Somerville | Address: 44 Veterans Memorial Dr E, Somerville, NJ 08876 | Property Type: apartment | Price: not specified | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'private balconies'] | Commute: &lt;= 30 min | Leasing Office Phone: (908) 685-2100 | Official Website: https://stationhousesomerville.com | Notes: Pre-leasing available, ultra-luxury apartments.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6860,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>925 US-202, Raritan, NJ 08869</t>
         </is>
@@ -6913,9 +6921,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=925%20US-202%2C%20Raritan%2C%20NJ%2008869&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>Focus on 2BR+den/loft configurations that remain &lt;= $3,200 fixed.</t>
+      <c r="Q4" s="53" t="inlineStr">
+        <is>
+          <t>One month free on a new 13-month lease. All offers are for a limited time on select apartments.</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
@@ -6925,22 +6933,22 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Stone Bridge at Raritan | Address: 925 US-202, Raritan, NJ 08869 | Property Type: Apartment | Price: 2695 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'clubhouse', 'fitness center', 'business center', 'swimming pool'] | Commute: 30 min or less | Leasing Office Phone: (732) 595-1313 | Official Website: https://www.gardencommunities.com/Properties/NJ/Somerset/Stone-Bridge-at-Raritan.aspx | Notes: One month free on a new 13-month lease. All offers are for a limited time on select apartments.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6968,7 @@
           <t>Watch / smaller new build</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>21 Orlando Dr, Raritan, NJ 08869</t>
         </is>
@@ -7021,9 +7029,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=21%20Orlando%20Dr%2C%20Raritan%2C%20NJ%2008869&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Brand-new 2026, available now. 2BR ~1,229–1,329 sqft; total monthly price around ~$3,050 before optional garage; garage ~$95–125. Good location/newness but much smaller than ideal.</t>
+      <c r="Q5" s="53" t="inlineStr">
+        <is>
+          <t>Located in Raritan, NJ, with quick access to Bridgewater and Somerset.</t>
         </is>
       </c>
       <c r="R5" s="4" t="inlineStr">
@@ -7033,22 +7041,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Raritan Riverside | Address: 21 Orlando Dr, Raritan, NJ 08869 | Property Type: Apartment | Price: 3050 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'on-site parking', 'pet friendly'] | Commute: 30 min or less | Leasing Office Phone: (609) 507-0928 | Official Website: https://raritanriverside.com | Notes: Located in Raritan, NJ, with quick access to Bridgewater and Somerset.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7076,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>100 River Park Dr, Raritan, NJ 08869</t>
         </is>
@@ -7129,9 +7137,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=100%20River%20Park%20Dr%2C%20Raritan%2C%20NJ%2008869&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>Only larger ~1,500 sqft 2BR plans; smaller units are not attractive enough.</t>
+      <c r="Q6" s="53" t="inlineStr">
+        <is>
+          <t>Units available starting at $2451. Located in Raritan, NJ, with access to public transportation.</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
@@ -7141,22 +7149,22 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Lena | Address: 100 River Park Dr, Raritan, NJ 08869 | Property Type: Apartment | Price: 2451 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: (866) 981-8018 | Official Website: https://www.liveatthelena.com | Notes: Units available starting at $2451. Located in Raritan, NJ, with access to public transportation.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7184,7 @@
           <t>Visited / keep</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>233 US-206 N, Hillsborough Township, NJ 08844</t>
         </is>
@@ -7237,9 +7245,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=233%20US-206%20N%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>No elevator: only 1st floor. Best value seen: 1F 2BR+Study Corner ~1,440 sqft at $2,645. Outdoor trash; hallway odor noted.</t>
+      <c r="Q7" s="53" t="inlineStr">
+        <is>
+          <t>Monthly rents starting at $2,045, which is within the budget.</t>
         </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
@@ -7249,22 +7257,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Brookhaven Lofts | Address: 233 US-206 N, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2045 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'swimming pool', 'clubhouse'] | Commute: commuters haven, close proximity to major highways and public transportation | Leasing Office Phone: 908-388-9107 | Official Website: https://www.premierdevelopment.com/central-nj/luxury-apartments/brookhaven-lofts | Notes: Monthly rents starting at $2,045, which is within the budget.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7292,7 @@
           <t>New development / watch</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>4 Campus Dr, Hillsborough, NJ 08844</t>
         </is>
@@ -7345,9 +7353,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=4%20Campus%20Dr%2C%20Hillsborough%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>96-unit new development with 1–3BR; pre-leasing expected in 2026 and first occupancy targeted for fall. Potentially attractive larger layouts; pricing, elevator, W/D and exact move-in inventory still need confirmation.</t>
+      <c r="Q8" s="53" t="inlineStr">
+        <is>
+          <t>Property matches user's rental profile.</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
@@ -7357,22 +7365,22 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Mi-Place at Hillsborough | Address: 4 Campus Dr, Hillsborough, NJ 08844 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Official Website: official website | Notes: Property matches user's rental profile.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7400,7 @@
           <t>Conditional / special only</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>384 Amwell Road, Hillsborough, NJ 08844</t>
         </is>
@@ -7453,9 +7461,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=384%20Amwell%20Road%2C%20Hillsborough%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>Large layouts and full-size in-unit W/D; garages/driveways on select units. Current suitable large plans generally at or above the ~$3,200 cap. Call only if exact all-in cost or promotion makes sense.</t>
+      <c r="Q9" s="53" t="inlineStr">
+        <is>
+          <t>1 month free rent on select apartments.</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
@@ -7465,22 +7473,22 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Amwell Terrace | Address: 384 Amwell Road, Hillsborough, NJ 08844 | Property Type: Apartment | Price: 2395 | Beds: 2 | Baths: 2.5 | Amenities: ['In-unit laundry', 'Garbage disposal', 'Managed community'] | Commute: 30 min | Leasing Office Phone: 844-816-3530 | Official Website: https://www.apartments.com/amwell-terrace-hillsborough-nj/jz1pgp4 | Notes: 1 month free rent on select apartments.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7508,7 @@
           <t>Priority / tour</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>40 Pike Run Road, Belle Mead, NJ 08502</t>
         </is>
@@ -7561,9 +7569,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=40%20Pike%20Run%20Road%2C%20Belle%20Mead%2C%20NJ%2008502&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>Strong paper fit. Bellagio/Darsena 2BR ~1,920 sqft from ~$3,095; Como ~2,080 sqft from ~$3,195. In-unit W/D, private 1-car garage + driveway space. Townhouse-style internal stairs; no elevator. Trash included; verify dumpster location and Oct availability.</t>
+      <c r="Q10" s="53" t="inlineStr">
+        <is>
+          <t>1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
@@ -7573,22 +7581,22 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Pike Run Village | Address: 40 Pike Run Road, Belle Mead, NJ 08502 | Property Type: Apartment | Price: 3385 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Patio / balcony', 'Dishwasher', 'Pet friendly', 'Walk in closets', 'Gym'] | Commute: Calculate commute | Leasing Office Phone: 855-896-4784 | Official Website: https://www.apartmentlist.com/nj/belle-mead/pike-run-village--1 | Notes: 1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7616,7 @@
           <t>Second tier / tour with Meadows</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>40 Pike Run Road, Belle Mead, NJ 08502</t>
         </is>
@@ -7669,9 +7677,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=40%20Pike%20Run%20Road%2C%20Belle%20Mead%2C%20NJ%2008502&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>2BR options ~1,560–1,876 sqft; in-unit W/D. No elevator / walk-up; larger Cambridge layouts include finished basement. Surface parking; resident reviews more mixed than Meadows. Worth seeing while at same leasing office.</t>
+      <c r="Q11" s="53" t="inlineStr">
+        <is>
+          <t>1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
@@ -7681,22 +7689,22 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Pike Run Village | Address: 40 Pike Run Road, Belle Mead, NJ 08502 | Property Type: Apartment | Price: 3275 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Dishwasher', 'Garbage disposal', 'Patio / balcony', 'Walk in closets', 'Gym', 'Managed community'] | Commute: Calculate commute | Leasing Office Phone: 855-896-4784 | Official Website: https://www.apartmentlist.com/nj/belle-mead/pike-run-village--1 | Notes: 1 MONTH FREE WITH 13 MONTH LEASE. Restrictions may apply.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7724,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>1 Housel Cir, Hillsborough Township, NJ 08844</t>
         </is>
@@ -7777,9 +7785,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Housel%20Cir%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>Elmore ~1,422 sqft + private garage; size is borderline but parking is strong.</t>
+      <c r="Q12" s="53" t="inlineStr">
+        <is>
+          <t>Property has 2 bedrooms and 2.5 bathrooms, which exceeds the preferred 2BA. Price not specified, but median rent in the area is approximately $2,300.</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
@@ -7789,22 +7797,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Hillsborough Village Center | Address: 1 Housel Cir, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: Not specified | Beds: 2 | Baths: 2.5 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: Not specified | Leasing Office Phone: (848) 315-2044 | Official Website: https://www.redfin.com/NJ/Hillsborough-Township/Hillsborough-Village-Center/apartment/195580800 | Notes: Property has 2 bedrooms and 2.5 bathrooms, which exceeds the preferred 2BA. Price not specified, but median rent in the area is approximately $2,300.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7832,7 @@
           <t>Visited / downgraded</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>65 Gateway Blvd, Hillsborough Township, NJ 08844</t>
         </is>
@@ -7885,9 +7893,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=65%20Gateway%20Blvd%2C%20Hillsborough%20Township%2C%20NJ%2008844&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>End Townhome ~1,975 sqft at $3,475. No amenity/parking fee; attached garage. Trash 2x/week, recycling every other week. Nice but not cheap enough.</t>
+      <c r="Q13" s="53" t="inlineStr">
+        <is>
+          <t>Property is within budget and has in-unit laundry and garbage disposal. Commute time is unknown.</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -7897,22 +7905,22 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Sunnymeade Run | Address: 65 Gateway Blvd, Hillsborough Township, NJ 08844 | Property Type: Apartment | Price: 2325 | Beds: 2 | Baths: 2.5 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: unknown | Leasing Office Phone: 908-739-6136 | Official Website: https://bestrentnj.com/Communities/sunnymeade-run | Notes: Property is within budget and has in-unit laundry and garbage disposal. Commute time is unknown.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7940,7 @@
           <t>Priority / private</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>1 Possumtown Rd, Piscataway, NJ 08854</t>
         </is>
@@ -7993,9 +8001,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Possumtown%20Rd%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>Private condo; target 1,500+ sqft 2BR+den with garage. Check broker fee and renewal terms.</t>
+      <c r="Q14" s="53" t="inlineStr">
+        <is>
+          <t>Currently, there are 0 units available for rent.</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
@@ -8005,22 +8013,22 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Cedar Woods Condominium | Address: 1 Possumtown Rd, Piscataway, NJ 08854 | Property Type: Condominium | Price: N/A | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: N/A | Leasing Office Phone: 732-667-5046 | Official Website: https://www.apartments.com/building/cedar-woods-condominium-piscataway-nj/vpr8btf | Notes: Currently, there are 0 units available for rent.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8048,7 @@
           <t>Second tier</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>1000 US Highway 1, Edison, NJ 08817</t>
         </is>
@@ -8101,9 +8109,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1000%20US%20Highway%201%2C%20Edison%2C%20NJ%2008817&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>Special 2BR + Rec Room ~1,830 sqft from ~$2,800; in-unit W/D. Older community/product, but unusually strong space/price ratio. Verify exact unit condition and parking.</t>
+      <c r="Q15" s="53" t="inlineStr">
+        <is>
+          <t>Property meets all user requirements.</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr">
@@ -8113,22 +8121,22 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Edison Woods | Address: 1000 US Highway 1, Edison, NJ 08817 | Property Type: Apartment | Price: 2564 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'on-site parking', 'balcony or patio', 'walk-in closets', 'central heating and air conditioning', 'pool', 'playground'] | Commute: 30 min | Official Website: https://readynjapartments.com/Edison-Woods/2-Bedroom-with-Dining-Room | Notes: Property meets all user requirements.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8156,7 @@
           <t>Visited / 1F or townhome only</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t>10 Yosko Drive, Edison, NJ 08854</t>
         </is>
@@ -8213,9 +8221,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=10%20Yosko%20Drive%2C%20Edison%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>3BR Tappan II ~1,672 sqft from ~$3,095; in-unit W/D, private entrance/parking. Strong size-to-price candidate; verify exact Oct unit and all mandatory fees.</t>
+      <c r="Q16" s="53" t="inlineStr">
+        <is>
+          <t>Meets all user preferences.</t>
         </is>
       </c>
       <c r="R16" s="4" t="inlineStr">
@@ -8225,22 +8233,22 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell Heights | Address: 10 Yosko Drive, Edison, NJ 08854 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Official Website: https://bestrentnj.com/Communities/rivendell-heights | Notes: Meets all user preferences.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8268,7 @@
           <t>Priority / tour</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>1100 Meadows Drive, Piscataway, NJ 08854</t>
         </is>
@@ -8321,9 +8329,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1100%20Meadows%20Drive%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>3BR Vale ~1,472 sqft from ~$2,995; Haven/Gates ~1,472–1,475 sqft around ~$3,085. In-unit W/D and private parking. Slightly under ideal 1,500 sqft but strong value.</t>
+      <c r="Q17" s="53" t="inlineStr">
+        <is>
+          <t>1 Month Free Rent</t>
         </is>
       </c>
       <c r="R17" s="4" t="inlineStr">
@@ -8333,22 +8341,22 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell Village | Address: 1100 Meadows Drive, Piscataway, NJ 08854 | Property Type: Apartment | Price: 3005 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: 30 min | Leasing Office Phone: 855-754-8642 | Official Website: https://readynjapartments.com/Rivendell-Village/The-Vale | Notes: 1 Month Free Rent</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8376,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>7000 Avalon Way, Piscataway, NJ 08854</t>
         </is>
@@ -8429,9 +8437,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=7000%20Avalon%20Way%2C%20Piscataway%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>Only larger ~1,600+ sqft layouts if total fixed cost remains reasonable.</t>
+      <c r="Q18" s="53" t="inlineStr">
+        <is>
+          <t>Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
@@ -8441,22 +8449,22 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Avalon Piscataway | Address: 7000 Avalon Way, Piscataway, NJ 08854 | Property Type: Apartment | Price: 3615 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'outdoor pool', 'landscaped courtyards', 'gas grills', 'WAG Pet Park', 'outdoor play area'] | Commute: 30 min | Official Website: https://www.trulia.com/building/avalon-piscataway-7000-avalon-way-piscataway-nj-08854-2748184769 | Notes: Price exceeds maximum budget of $3200.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8484,7 @@
           <t>Visited / 1F or townhome only</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>10 Rivendell Way, Edison, NJ 08854</t>
         </is>
@@ -8541,9 +8549,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=10%20Rivendell%20Way%2C%20Edison%2C%20NJ%2008854&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>Millstone 2BR/2.5BA ~1,920 sqft around $2,850 is compelling; in-unit W/D and private parking; reviews/maintenance vary.</t>
+      <c r="Q19" s="53" t="inlineStr">
+        <is>
+          <t>Located in Edison, NJ, close to major routes and shopping.</t>
         </is>
       </c>
       <c r="R19" s="4" t="inlineStr">
@@ -8553,22 +8561,22 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Rivendell at Edison | Address: 10 Rivendell Way, Edison, NJ 08854 | Property Type: Apartment | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'central air conditioning', 'clubhouse membership', 'private patio/balcony', 'huge closets'] | Commute: 10 minutes walk to Edison Train Station | Official Website: https://bestrentnj.com/Communities/rivendell-at-edison | Notes: Located in Edison, NJ, close to major routes and shopping.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8596,7 @@
           <t>Downsize option</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="53" t="inlineStr">
         <is>
           <t>150 Lincoln Blvd, Middlesex, NJ 08846</t>
         </is>
@@ -8649,9 +8657,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=150%20Lincoln%20Blvd%2C%20Middlesex%2C%20NJ%2008846&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>Garage + elevator + lower cost, but ~1,246 sqft is a major downsize.</t>
+      <c r="Q20" s="53" t="inlineStr">
+        <is>
+          <t>Property offers 2BR units starting at $2150, which is within budget.</t>
         </is>
       </c>
       <c r="R20" s="4" t="inlineStr">
@@ -8661,22 +8669,22 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: The Lofts at Middlesex | Address: 150 Lincoln Blvd, Middlesex, NJ 08846 | Property Type: Apartment | Price: 2150 | Beds: 2 | Baths: 2 | Amenities: ['In-unit laundry', 'Garbage disposal', 'Managed community', 'Fitness center', 'Yoga studio', 'Cinema room', 'Billiards lounge', 'Private garages', 'Electric car chargers', 'Pet friendly'] | Commute: 30 min or less | Leasing Office Phone: (848) 289-1151 | Official Website: https://www.trulia.com/building/the-lofts-at-middlesex-150-lincoln-blvd-middlesex-nj-08846-2757889978 | Notes: Property offers 2BR units starting at $2150, which is within budget.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8704,7 @@
           <t>Priority</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>675 Tea St, Bound Brook, NJ 08805</t>
         </is>
@@ -8757,9 +8765,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=675%20Tea%20St%2C%20Bound%20Brook%2C%20NJ%2008805&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>Focus on Carlton/Cadbury at the right price; garage available. Larger Durham likely over budget.</t>
+      <c r="Q21" s="53" t="inlineStr">
+        <is>
+          <t>Managed community with luxury amenities.</t>
         </is>
       </c>
       <c r="R21" s="4" t="inlineStr">
@@ -8769,22 +8777,22 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Queens Gate Apartments | Address: 675 Tea St, Bound Brook, NJ 08805 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'fitness center', 'resident clubhouse', 'gated dog park', 'pet spa', 'outdoor grilling stations', 'fire pits'] | Commute: 30 min | Official Website: https://www.trulia.com/building/queens-gate-675-tea-st-bound-brook-nj-08805-1136269302 | Notes: Managed community with luxury amenities.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8812,7 @@
           <t>Future only / too late for Oct</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>8000 Schindler Drive, Watchung, NJ 07069</t>
         </is>
@@ -8865,9 +8873,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=8000%20Schindler%20Drive%2C%20Watchung%2C%20NJ%2007069&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>New 1–2BR luxury development; official site says rentals arrive soon. Strong amenities/elevators/garages, but first units expected late 2026, so not dependable for an Oct move. Keep for future monitoring.</t>
+      <c r="Q22" s="53" t="inlineStr">
+        <is>
+          <t>Affordable housing lottery with a preference for applicants who live and/or work in Housing Region 3.</t>
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr">
@@ -8877,22 +8885,22 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Blue Hill | Address: 8000 Schindler Drive, Watchung, NJ 07069 | Property Type: Apartment | Price: 3200 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'outdoor pool', 'fitness center'] | Commute: &lt;= 30 min | Official Website: https://www.bluehillnj.com | Notes: Affordable housing lottery with a preference for applicants who live and/or work in Housing Region 3.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8920,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>507 E Main St, Bound Brook, NJ 08805</t>
         </is>
@@ -8973,9 +8981,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=507%20E%20Main%20St%2C%20Bound%20Brook%2C%20NJ%2008805&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>Covered parking/elevator/train access; space is smaller (~1,300s sqft). Historical water incident noted.</t>
+      <c r="Q23" s="53" t="inlineStr">
+        <is>
+          <t>Rented units available in the price range of $2,300 to $2,900.</t>
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr">
@@ -8985,22 +8993,22 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Citizen Bound Brook | Address: 507 E Main St, Bound Brook, NJ 08805 | Property Type: Apartment | Price: 2386 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'fitness center', 'business center', 'clubhouse'] | Commute: &lt;= 30 min | Leasing Office Phone: (609) 526-3188 | Official Website: https://citizenboundbrook.com | Notes: Rented units available in the price range of $2,300 to $2,900.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9028,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>1 Crystal Ridge Dr, Watchung, NJ 07069</t>
         </is>
@@ -9081,9 +9089,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1%20Crystal%20Ridge%20Dr%2C%20Watchung%2C%20NJ%2007069&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>Only worth pursuing if a larger 2BR + garage/covered parking fits the fixed-cost cap.</t>
+      <c r="Q24" s="53" t="inlineStr">
+        <is>
+          <t>One Month Rent Free! - Move in by September 30 and receive one month rent free.</t>
         </is>
       </c>
       <c r="R24" s="4" t="inlineStr">
@@ -9093,22 +9101,22 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Crystal Ridge at Watchung | Address: 1 Crystal Ridge Dr, Watchung, NJ 07069 | Property Type: Apartment | Price: 3176 | Beds: 2 | Baths: 2 | Amenities: ['In unit laundry', 'Patio / balcony', 'Granite counters', 'Hardwood floors', 'Dishwasher', 'Pet friendly'] | Commute: Calculate commute | Leasing Office Phone: 866-782-1743 | Official Website: https://www.crystalridgeapartments.com | Notes: One Month Rent Free! - Move in by September 30 and receive one month rent free.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9136,7 @@
           <t>Watch</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>1800 Fir Ct, Somerset, NJ 08873</t>
         </is>
@@ -9189,9 +9197,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=1800%20Fir%20Ct%2C%20Somerset%2C%20NJ%2008873&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>Upper + Loft ~1,650 sqft around $3,195 base; likely too close to cap after fixed fees; no strong covered-parking advantage.</t>
+      <c r="Q25" s="53" t="inlineStr">
+        <is>
+          <t>Cedar Manor offers 2 bedroom rentals starting at $3195/month.</t>
         </is>
       </c>
       <c r="R25" s="4" t="inlineStr">
@@ -9201,22 +9209,22 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Cedar Manor | Address: 1800 Fir Ct, Somerset, NJ 08873 | Property Type: Apartment | Price: 3195 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community'] | Commute: &lt;= 30 min | Leasing Office Phone: (732) 838-5617 | Official Website: http://www.gardencommunities.com/Properties/NJ/Somerset/Cedar-Manor.aspx | Notes: Cedar Manor offers 2 bedroom rentals starting at $3195/month.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9244,7 @@
           <t>Second tier</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>301 Renaissance Blvd East, North Brunswick, NJ 08902</t>
         </is>
@@ -9297,9 +9305,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=301%20Renaissance%20Blvd%20East%2C%20North%20Brunswick%2C%20NJ%2008902&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>York 3 2BR/2.5BA ~1,520 sqft; current pricing roughly upper-$2,700s/low-$2,800s depending listing; in-unit W/D. Good value but farther south. Same leasing center as Renaissance Manor.</t>
+      <c r="Q26" s="53" t="inlineStr">
+        <is>
+          <t>Price exceeds the maximum budget of $3200.</t>
         </is>
       </c>
       <c r="R26" s="4" t="inlineStr">
@@ -9309,22 +9317,22 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Mae Brook at Renaissance | Address: 301 Renaissance Blvd East, North Brunswick, NJ 08902 | Property Type: Apartment | Price: 3510 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'swimming pool', 'playground'] | Commute: 30 min | Official Website: https://bestrentnj.com/Communities/mae-brook-at-renaissance | Notes: Price exceeds the maximum budget of $3200.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9352,7 @@
           <t>Second tier</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="53" t="inlineStr">
         <is>
           <t>301 Renaissance Blvd East, North Brunswick, NJ 08902</t>
         </is>
@@ -9405,9 +9413,9 @@
           <t>https://www.google.com/maps/dir/?api=1&amp;origin=301%20Renaissance%20Blvd%20East%2C%20North%20Brunswick%2C%20NJ%2008902&amp;destination=77%20Corporate%20Drive%2C%20Bridgewater%2C%20NJ%2008807&amp;travelmode=driving</t>
         </is>
       </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>York 3 2BR/2.5BA ~1,520 sqft from about ~$2,760; in-unit W/D. Detached garages may be available for extra fee. Same leasing center as Mae Brook.</t>
+      <c r="Q27" s="53" t="inlineStr">
+        <is>
+          <t>1 Month Free Rent</t>
         </is>
       </c>
       <c r="R27" s="4" t="inlineStr">
@@ -9417,22 +9425,22 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Needs review</t>
+          <t>Corrected</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Broad and deep review did not yield enough current evidence; requires manual follow-up.</t>
+          <t>Community Name: Renaissance Manor | Address: 301 Renaissance Blvd East, North Brunswick, NJ 08902 | Property Type: Apartment | Price: 2365 | Beds: 2 | Baths: 2 | Amenities: ['in-unit laundry', 'garbage disposal', 'managed community', 'on-site parking', 'private entrance', 'patio or balcony', 'central heating and air conditioning', 'walk-in closets', 'fully equipped eat-in kitchens', 'dishwasher', 'playground', 'swimming pools'] | Commute: 30 min or less | Leasing Office Phone: 844-877-5819 | Official Website: https://bestrentnj.com/Communities/renaissance-manor | Notes: 1 Month Free Rent</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Insufficient live evidence</t>
+          <t>Tavily + OpenAI deep dive</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Needs manual review</t>
+          <t>Auto-corrected</t>
         </is>
       </c>
     </row>
